--- a/output/quickfixopen2_portfolio_daily.xlsx
+++ b/output/quickfixopen2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>414,063.40</t>
+          <t>422,418.74</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+314.06%</t>
+          <t>+322.42%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>426,539  (+326.54%)</t>
+          <t>435,299  (+335.30%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,501  (12.5 pts of return)</t>
+          <t>5,653  (12.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26.8x</t>
+          <t>27.5x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.57R  (best +16.36R)</t>
+          <t>+3.54R  (best +16.36R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,790  (+3.57%)</t>
+          <t>6,815  (+3.54%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>54% of trading days</t>
+          <t>55% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5507,22 +5507,50 @@
         <v>46233</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>414063.4</v>
+        <v>414215.32</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>0</v>
+        <v>3797.88</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>414063.4</v>
+        <v>410417.44</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_open (+31,064)</t>
+          <t>US_Dollar_Index_Futures exit_open (+31,064)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures exit_open (+8,203)</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10080,7 @@
         <v>65407.25</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>673808.08</v>
+        <v>674142.6</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -10076,14 +10104,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G89" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.04</v>
+        <v>2.16</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>601654.72</v>
@@ -10091,15 +10127,15 @@
       <c r="J89" s="5" t="n">
         <v>8363</v>
       </c>
-      <c r="K89" s="7" t="n">
-        <v>-334.52</v>
+      <c r="K89" s="6" t="n">
+        <v>18064.08</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>608400.83</v>
+        <v>692206.6800000001</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_open</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen2_portfolio_daily.xlsx
+++ b/output/quickfixopen2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>55% of trading days</t>
+          <t>54% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5553,6 +5553,46 @@
           <t>NY_Natural_Gas_Futures exit_open (+8,203)</t>
         </is>
       </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixopen2_portfolio_daily.xlsx
+++ b/output/quickfixopen2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>422,418.74</t>
+          <t>422,395.96</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+322.42%</t>
+          <t>+322.40%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,653  (12.9 pts of return)</t>
+          <t>5,676  (12.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5594,6 +5594,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>422418.74</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12546.26</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>409872.48</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 4,224); Nasdaq_100_E_mini short (risk 4,182); S_P_500_E_mini short (risk 4,140)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>422395.96</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>422395.96</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 4,099)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5606,7 +5662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10179,6 +10235,178 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>692206.6800000001</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>9621.67</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>-33.41</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>692156.98</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>682585.01</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>9487.93</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>692190.39</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>673097.08</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>9356.049999999999</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>692155</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>663741.03</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>9226</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>692190.91</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixopen2_portfolio_daily.xlsx
+++ b/output/quickfixopen2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>422,395.96</t>
+          <t>434,244.27</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+322.40%</t>
+          <t>+334.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>435,299  (+335.30%)</t>
+          <t>447,574  (+347.57%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,676  (12.9 pts of return)</t>
+          <t>5,740  (13.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27.5x</t>
+          <t>28.6x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.54R  (best +16.36R)</t>
+          <t>+3.43R  (best +16.36R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,815  (+3.54%)</t>
+          <t>6,741  (+3.43%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-2,130  (-1.40%)</t>
+          <t>-2,193  (-1.39%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5627,26 +5627,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>422395.96</v>
+        <v>422418.74</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>0</v>
+        <v>16644.98</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>422395.96</v>
+        <v>405773.76</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>Gold_Futures_COMEX short (risk 4,099)</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>434244.27</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>434244.27</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 4,058); NY_Palladium_Futures short (risk 4,017)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-4,127); Nasdaq_100_E_mini exit_open (+8,736); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures exit_open (+3,916); S_P_500_E_mini exit_open (+3,327)</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10251,14 +10279,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.003</v>
+        <v>0.927</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>692206.6800000001</v>
@@ -10266,15 +10302,15 @@
       <c r="J90" s="5" t="n">
         <v>9621.67</v>
       </c>
-      <c r="K90" s="7" t="n">
-        <v>-33.41</v>
+      <c r="K90" s="6" t="n">
+        <v>8919.83</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>692156.98</v>
+        <v>711596.9</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_open</t>
         </is>
       </c>
     </row>
@@ -10294,14 +10330,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-0</v>
+        <v>2.089</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>682585.01</v>
@@ -10309,15 +10353,15 @@
       <c r="J91" s="5" t="n">
         <v>9487.93</v>
       </c>
-      <c r="K91" s="7" t="n">
-        <v>-0.52</v>
+      <c r="K91" s="6" t="n">
+        <v>19819.24</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>692190.39</v>
+        <v>702736.84</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_open</t>
         </is>
       </c>
     </row>
@@ -10337,14 +10381,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>0.804</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-0</v>
+        <v>0.804</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>673097.08</v>
@@ -10352,15 +10404,15 @@
       <c r="J92" s="5" t="n">
         <v>9356.049999999999</v>
       </c>
-      <c r="K92" s="7" t="n">
-        <v>-1.98</v>
+      <c r="K92" s="6" t="n">
+        <v>7519.24</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>692155</v>
+        <v>719116.14</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_open</t>
         </is>
       </c>
     </row>
@@ -10380,14 +10432,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>663741.03</v>
@@ -10396,12 +10456,98 @@
         <v>9226</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>-15.77</v>
+        <v>-9289.08</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>692190.91</v>
+        <v>682917.6</v>
       </c>
       <c r="M93" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>654515.03</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>9097.76</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>-24.59</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>702712.25</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>645417.27</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>8971.299999999999</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>-35.18</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>702677.0699999999</v>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
